--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135708128</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135708153</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135708118</v>
       </c>
       <c r="B4" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135708109</v>
       </c>
       <c r="B5" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135708115</v>
       </c>
       <c r="B6" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135708122</v>
       </c>
       <c r="B7" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135708123</v>
       </c>
       <c r="B8" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135708129</v>
       </c>
       <c r="B9" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135708130</v>
       </c>
       <c r="B10" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135708132</v>
       </c>
       <c r="B11" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135708133</v>
       </c>
       <c r="B12" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135708134</v>
       </c>
       <c r="B13" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135708136</v>
       </c>
       <c r="B14" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135708137</v>
       </c>
       <c r="B15" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135708139</v>
       </c>
       <c r="B16" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135708140</v>
       </c>
       <c r="B17" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135708177</v>
       </c>
       <c r="B18" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135708179</v>
       </c>
       <c r="B19" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135708182</v>
       </c>
       <c r="B20" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135708183</v>
       </c>
       <c r="B21" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135708185</v>
       </c>
       <c r="B22" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135708190</v>
       </c>
       <c r="B23" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135708131</v>
       </c>
       <c r="B24" t="n">
-        <v>92989</v>
+        <v>92991</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135708158</v>
       </c>
       <c r="B25" t="n">
-        <v>92989</v>
+        <v>92991</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135708166</v>
       </c>
       <c r="B26" t="n">
-        <v>92989</v>
+        <v>92991</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135708186</v>
       </c>
       <c r="B27" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135708150</v>
       </c>
       <c r="B32" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135708151</v>
       </c>
       <c r="B33" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135708154</v>
       </c>
       <c r="B34" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135708156</v>
       </c>
       <c r="B35" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135708157</v>
       </c>
       <c r="B36" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135708159</v>
       </c>
       <c r="B37" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135708128</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135708153</v>
       </c>
       <c r="B3" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135708118</v>
       </c>
       <c r="B4" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135708109</v>
       </c>
       <c r="B5" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135708115</v>
       </c>
       <c r="B6" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135708122</v>
       </c>
       <c r="B7" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135708123</v>
       </c>
       <c r="B8" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135708129</v>
       </c>
       <c r="B9" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135708130</v>
       </c>
       <c r="B10" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135708132</v>
       </c>
       <c r="B11" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135708133</v>
       </c>
       <c r="B12" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135708134</v>
       </c>
       <c r="B13" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135708136</v>
       </c>
       <c r="B14" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135708137</v>
       </c>
       <c r="B15" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135708139</v>
       </c>
       <c r="B16" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135708140</v>
       </c>
       <c r="B17" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135708177</v>
       </c>
       <c r="B18" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135708179</v>
       </c>
       <c r="B19" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135708182</v>
       </c>
       <c r="B20" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135708183</v>
       </c>
       <c r="B21" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135708185</v>
       </c>
       <c r="B22" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135708190</v>
       </c>
       <c r="B23" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135708131</v>
       </c>
       <c r="B24" t="n">
-        <v>92991</v>
+        <v>93006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135708158</v>
       </c>
       <c r="B25" t="n">
-        <v>92991</v>
+        <v>93006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135708166</v>
       </c>
       <c r="B26" t="n">
-        <v>92991</v>
+        <v>93006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135708186</v>
       </c>
       <c r="B27" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135708116</v>
       </c>
       <c r="B28" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135708108</v>
       </c>
       <c r="B29" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135708125</v>
       </c>
       <c r="B30" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135708167</v>
       </c>
       <c r="B31" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135708150</v>
       </c>
       <c r="B32" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135708151</v>
       </c>
       <c r="B33" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135708154</v>
       </c>
       <c r="B34" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135708156</v>
       </c>
       <c r="B35" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135708157</v>
       </c>
       <c r="B36" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135708159</v>
       </c>
       <c r="B37" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135708111</v>
       </c>
       <c r="B38" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135708121</v>
       </c>
       <c r="B39" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135708138</v>
       </c>
       <c r="B40" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135708162</v>
       </c>
       <c r="B41" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135708168</v>
       </c>
       <c r="B42" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135708128</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135708153</v>
       </c>
       <c r="B3" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135708118</v>
       </c>
       <c r="B4" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135708109</v>
       </c>
       <c r="B5" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135708115</v>
       </c>
       <c r="B6" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135708122</v>
       </c>
       <c r="B7" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135708123</v>
       </c>
       <c r="B8" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135708129</v>
       </c>
       <c r="B9" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135708130</v>
       </c>
       <c r="B10" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135708132</v>
       </c>
       <c r="B11" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135708133</v>
       </c>
       <c r="B12" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135708134</v>
       </c>
       <c r="B13" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135708136</v>
       </c>
       <c r="B14" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135708137</v>
       </c>
       <c r="B15" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135708139</v>
       </c>
       <c r="B16" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135708140</v>
       </c>
       <c r="B17" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135708177</v>
       </c>
       <c r="B18" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135708179</v>
       </c>
       <c r="B19" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135708182</v>
       </c>
       <c r="B20" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135708183</v>
       </c>
       <c r="B21" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135708185</v>
       </c>
       <c r="B22" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135708190</v>
       </c>
       <c r="B23" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135708131</v>
       </c>
       <c r="B24" t="n">
-        <v>93006</v>
+        <v>93007</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135708158</v>
       </c>
       <c r="B25" t="n">
-        <v>93006</v>
+        <v>93007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135708166</v>
       </c>
       <c r="B26" t="n">
-        <v>93006</v>
+        <v>93007</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135708186</v>
       </c>
       <c r="B27" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135708116</v>
       </c>
       <c r="B28" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135708108</v>
       </c>
       <c r="B29" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135708125</v>
       </c>
       <c r="B30" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135708150</v>
       </c>
       <c r="B32" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135708151</v>
       </c>
       <c r="B33" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135708154</v>
       </c>
       <c r="B34" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135708156</v>
       </c>
       <c r="B35" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135708157</v>
       </c>
       <c r="B36" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135708159</v>
       </c>
       <c r="B37" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135708111</v>
       </c>
       <c r="B38" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135708121</v>
       </c>
       <c r="B39" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135708138</v>
       </c>
       <c r="B40" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135708162</v>
       </c>
       <c r="B41" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135708168</v>
       </c>
       <c r="B42" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135708128</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135708153</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135708118</v>
       </c>
       <c r="B4" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135708109</v>
       </c>
       <c r="B5" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135708115</v>
       </c>
       <c r="B6" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135708122</v>
       </c>
       <c r="B7" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135708123</v>
       </c>
       <c r="B8" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135708129</v>
       </c>
       <c r="B9" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135708130</v>
       </c>
       <c r="B10" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135708132</v>
       </c>
       <c r="B11" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135708133</v>
       </c>
       <c r="B12" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135708134</v>
       </c>
       <c r="B13" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135708136</v>
       </c>
       <c r="B14" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135708137</v>
       </c>
       <c r="B15" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135708139</v>
       </c>
       <c r="B16" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135708140</v>
       </c>
       <c r="B17" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135708177</v>
       </c>
       <c r="B18" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135708179</v>
       </c>
       <c r="B19" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135708182</v>
       </c>
       <c r="B20" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135708183</v>
       </c>
       <c r="B21" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135708185</v>
       </c>
       <c r="B22" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135708190</v>
       </c>
       <c r="B23" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135708131</v>
       </c>
       <c r="B24" t="n">
-        <v>93007</v>
+        <v>93008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135708158</v>
       </c>
       <c r="B25" t="n">
-        <v>93007</v>
+        <v>93008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135708166</v>
       </c>
       <c r="B26" t="n">
-        <v>93007</v>
+        <v>93008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135708186</v>
       </c>
       <c r="B27" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135708150</v>
       </c>
       <c r="B32" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135708151</v>
       </c>
       <c r="B33" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135708154</v>
       </c>
       <c r="B34" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135708156</v>
       </c>
       <c r="B35" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135708157</v>
       </c>
       <c r="B36" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135708159</v>
       </c>
       <c r="B37" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135708128</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135708153</v>
       </c>
       <c r="B3" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135708118</v>
       </c>
       <c r="B4" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135708109</v>
       </c>
       <c r="B5" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135708115</v>
       </c>
       <c r="B6" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135708122</v>
       </c>
       <c r="B7" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135708123</v>
       </c>
       <c r="B8" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135708129</v>
       </c>
       <c r="B9" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135708130</v>
       </c>
       <c r="B10" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135708132</v>
       </c>
       <c r="B11" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135708133</v>
       </c>
       <c r="B12" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135708134</v>
       </c>
       <c r="B13" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135708136</v>
       </c>
       <c r="B14" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135708137</v>
       </c>
       <c r="B15" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135708139</v>
       </c>
       <c r="B16" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135708140</v>
       </c>
       <c r="B17" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135708177</v>
       </c>
       <c r="B18" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135708179</v>
       </c>
       <c r="B19" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135708182</v>
       </c>
       <c r="B20" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135708183</v>
       </c>
       <c r="B21" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135708185</v>
       </c>
       <c r="B22" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135708190</v>
       </c>
       <c r="B23" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135708131</v>
       </c>
       <c r="B24" t="n">
-        <v>93008</v>
+        <v>93009</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135708158</v>
       </c>
       <c r="B25" t="n">
-        <v>93008</v>
+        <v>93009</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135708166</v>
       </c>
       <c r="B26" t="n">
-        <v>93008</v>
+        <v>93009</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135708186</v>
       </c>
       <c r="B27" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135708116</v>
       </c>
       <c r="B28" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135708108</v>
       </c>
       <c r="B29" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135708125</v>
       </c>
       <c r="B30" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135708167</v>
       </c>
       <c r="B31" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135708150</v>
       </c>
       <c r="B32" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135708151</v>
       </c>
       <c r="B33" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135708154</v>
       </c>
       <c r="B34" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135708156</v>
       </c>
       <c r="B35" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135708157</v>
       </c>
       <c r="B36" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135708159</v>
       </c>
       <c r="B37" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135708111</v>
       </c>
       <c r="B38" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135708121</v>
       </c>
       <c r="B39" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135708138</v>
       </c>
       <c r="B40" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135708162</v>
       </c>
       <c r="B41" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135708168</v>
       </c>
       <c r="B42" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135708128</v>
       </c>
       <c r="B2" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135708153</v>
       </c>
       <c r="B3" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135708118</v>
       </c>
       <c r="B4" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135708109</v>
       </c>
       <c r="B5" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135708115</v>
       </c>
       <c r="B6" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135708122</v>
       </c>
       <c r="B7" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135708123</v>
       </c>
       <c r="B8" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135708129</v>
       </c>
       <c r="B9" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135708130</v>
       </c>
       <c r="B10" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135708132</v>
       </c>
       <c r="B11" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135708133</v>
       </c>
       <c r="B12" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135708134</v>
       </c>
       <c r="B13" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135708136</v>
       </c>
       <c r="B14" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135708137</v>
       </c>
       <c r="B15" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135708139</v>
       </c>
       <c r="B16" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135708140</v>
       </c>
       <c r="B17" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135708177</v>
       </c>
       <c r="B18" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135708179</v>
       </c>
       <c r="B19" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135708182</v>
       </c>
       <c r="B20" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135708183</v>
       </c>
       <c r="B21" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135708185</v>
       </c>
       <c r="B22" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135708190</v>
       </c>
       <c r="B23" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135708131</v>
       </c>
       <c r="B24" t="n">
-        <v>93009</v>
+        <v>93015</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135708158</v>
       </c>
       <c r="B25" t="n">
-        <v>93009</v>
+        <v>93015</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135708166</v>
       </c>
       <c r="B26" t="n">
-        <v>93009</v>
+        <v>93015</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135708186</v>
       </c>
       <c r="B27" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135708116</v>
       </c>
       <c r="B28" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135708108</v>
       </c>
       <c r="B29" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135708125</v>
       </c>
       <c r="B30" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135708167</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135708150</v>
       </c>
       <c r="B32" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135708151</v>
       </c>
       <c r="B33" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135708154</v>
       </c>
       <c r="B34" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135708156</v>
       </c>
       <c r="B35" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135708157</v>
       </c>
       <c r="B36" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135708159</v>
       </c>
       <c r="B37" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135708111</v>
       </c>
       <c r="B38" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135708121</v>
       </c>
       <c r="B39" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135708138</v>
       </c>
       <c r="B40" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135708162</v>
       </c>
       <c r="B41" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135708168</v>
       </c>
       <c r="B42" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135708128</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135708153</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135708118</v>
       </c>
       <c r="B4" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135708109</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135708115</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135708122</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135708123</v>
       </c>
       <c r="B8" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135708129</v>
       </c>
       <c r="B9" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135708130</v>
       </c>
       <c r="B10" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135708132</v>
       </c>
       <c r="B11" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135708133</v>
       </c>
       <c r="B12" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135708134</v>
       </c>
       <c r="B13" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135708136</v>
       </c>
       <c r="B14" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135708137</v>
       </c>
       <c r="B15" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135708139</v>
       </c>
       <c r="B16" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135708140</v>
       </c>
       <c r="B17" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135708177</v>
       </c>
       <c r="B18" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135708179</v>
       </c>
       <c r="B19" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135708182</v>
       </c>
       <c r="B20" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135708183</v>
       </c>
       <c r="B21" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135708185</v>
       </c>
       <c r="B22" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135708190</v>
       </c>
       <c r="B23" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135708131</v>
       </c>
       <c r="B24" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135708158</v>
       </c>
       <c r="B25" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135708166</v>
       </c>
       <c r="B26" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135708186</v>
       </c>
       <c r="B27" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135708116</v>
       </c>
       <c r="B28" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135708108</v>
       </c>
       <c r="B29" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135708125</v>
       </c>
       <c r="B30" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135708167</v>
       </c>
       <c r="B31" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135708150</v>
       </c>
       <c r="B32" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135708151</v>
       </c>
       <c r="B33" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135708154</v>
       </c>
       <c r="B34" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135708156</v>
       </c>
       <c r="B35" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135708157</v>
       </c>
       <c r="B36" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135708159</v>
       </c>
       <c r="B37" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135708111</v>
       </c>
       <c r="B38" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135708121</v>
       </c>
       <c r="B39" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135708138</v>
       </c>
       <c r="B40" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135708162</v>
       </c>
       <c r="B41" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135708168</v>
       </c>
       <c r="B42" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135708128</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135708153</v>
       </c>
       <c r="B3" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135708118</v>
       </c>
       <c r="B4" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135708109</v>
       </c>
       <c r="B5" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135708115</v>
       </c>
       <c r="B6" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135708122</v>
       </c>
       <c r="B7" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135708123</v>
       </c>
       <c r="B8" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135708129</v>
       </c>
       <c r="B9" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135708130</v>
       </c>
       <c r="B10" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135708132</v>
       </c>
       <c r="B11" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135708133</v>
       </c>
       <c r="B12" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135708134</v>
       </c>
       <c r="B13" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135708136</v>
       </c>
       <c r="B14" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135708137</v>
       </c>
       <c r="B15" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135708139</v>
       </c>
       <c r="B16" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135708140</v>
       </c>
       <c r="B17" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135708177</v>
       </c>
       <c r="B18" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135708179</v>
       </c>
       <c r="B19" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135708182</v>
       </c>
       <c r="B20" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135708183</v>
       </c>
       <c r="B21" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135708185</v>
       </c>
       <c r="B22" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135708190</v>
       </c>
       <c r="B23" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135708131</v>
       </c>
       <c r="B24" t="n">
-        <v>93016</v>
+        <v>93022</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135708158</v>
       </c>
       <c r="B25" t="n">
-        <v>93016</v>
+        <v>93022</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135708166</v>
       </c>
       <c r="B26" t="n">
-        <v>93016</v>
+        <v>93022</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135708186</v>
       </c>
       <c r="B27" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135708116</v>
       </c>
       <c r="B28" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135708108</v>
       </c>
       <c r="B29" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135708125</v>
       </c>
       <c r="B30" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135708150</v>
       </c>
       <c r="B32" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135708151</v>
       </c>
       <c r="B33" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135708154</v>
       </c>
       <c r="B34" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>135708156</v>
       </c>
       <c r="B35" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>135708157</v>
       </c>
       <c r="B36" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>135708159</v>
       </c>
       <c r="B37" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>135708111</v>
       </c>
       <c r="B38" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>135708121</v>
       </c>
       <c r="B39" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>135708138</v>
       </c>
       <c r="B40" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>135708162</v>
       </c>
       <c r="B41" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>135708168</v>
       </c>
       <c r="B42" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4040,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135708150</v>
+        <v>135708112</v>
       </c>
       <c r="B32" t="n">
-        <v>98182</v>
+        <v>57180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4051,37 +4051,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Parkajoki, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855518</v>
+        <v>855779</v>
       </c>
       <c r="R32" t="n">
-        <v>7538734</v>
+        <v>7538233</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,7 +4115,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4120,7 +4125,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4146,16 +4151,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708150</t>
+          <t>https://artportalen.se/Sighting/135708112</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135708151</v>
+        <v>135708120</v>
       </c>
       <c r="B33" t="n">
-        <v>98182</v>
+        <v>57180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,21 +4168,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4187,10 +4192,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855495</v>
+        <v>855783</v>
       </c>
       <c r="R33" t="n">
-        <v>7538747</v>
+        <v>7538249</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4222,7 +4227,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4232,7 +4237,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4258,16 +4263,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708151</t>
+          <t>https://artportalen.se/Sighting/135708120</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135708154</v>
+        <v>135708141</v>
       </c>
       <c r="B34" t="n">
-        <v>98182</v>
+        <v>57180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,21 +4280,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4299,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855402</v>
+        <v>855636</v>
       </c>
       <c r="R34" t="n">
-        <v>7538970</v>
+        <v>7538526</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4334,7 +4339,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4344,7 +4349,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4370,16 +4375,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708154</t>
+          <t>https://artportalen.se/Sighting/135708141</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135708156</v>
+        <v>135708144</v>
       </c>
       <c r="B35" t="n">
-        <v>98182</v>
+        <v>57180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4387,21 +4392,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4411,10 +4416,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855399</v>
+        <v>855598</v>
       </c>
       <c r="R35" t="n">
-        <v>7538944</v>
+        <v>7538587</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4446,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4456,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4482,16 +4487,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708156</t>
+          <t>https://artportalen.se/Sighting/135708144</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135708157</v>
+        <v>135708145</v>
       </c>
       <c r="B36" t="n">
-        <v>98182</v>
+        <v>57180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4499,21 +4504,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855322</v>
+        <v>855596</v>
       </c>
       <c r="R36" t="n">
-        <v>7538890</v>
+        <v>7538594</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4558,7 +4563,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4573,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4594,16 +4599,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708157</t>
+          <t>https://artportalen.se/Sighting/135708145</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135708159</v>
+        <v>135708188</v>
       </c>
       <c r="B37" t="n">
-        <v>98182</v>
+        <v>57180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4611,21 +4616,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4635,10 +4640,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855323</v>
+        <v>855730</v>
       </c>
       <c r="R37" t="n">
-        <v>7538767</v>
+        <v>7538412</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4670,7 +4675,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4680,7 +4685,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4706,38 +4711,38 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708159</t>
+          <t>https://artportalen.se/Sighting/135708188</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135708111</v>
+        <v>135708191</v>
       </c>
       <c r="B38" t="n">
-        <v>79477</v>
+        <v>57180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>260591</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4747,10 +4752,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855791</v>
+        <v>855761</v>
       </c>
       <c r="R38" t="n">
-        <v>7538224</v>
+        <v>7538312</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4782,7 +4787,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4792,7 +4797,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4818,38 +4823,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708111</t>
+          <t>https://artportalen.se/Sighting/135708191</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135708121</v>
+        <v>135708150</v>
       </c>
       <c r="B39" t="n">
-        <v>79477</v>
+        <v>98182</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4859,10 +4864,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855784</v>
+        <v>855518</v>
       </c>
       <c r="R39" t="n">
-        <v>7538250</v>
+        <v>7538734</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4894,7 +4899,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4904,7 +4909,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4930,38 +4935,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708121</t>
+          <t>https://artportalen.se/Sighting/135708150</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135708138</v>
+        <v>135708151</v>
       </c>
       <c r="B40" t="n">
-        <v>79477</v>
+        <v>98182</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4971,10 +4976,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855768</v>
+        <v>855495</v>
       </c>
       <c r="R40" t="n">
-        <v>7538350</v>
+        <v>7538747</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5006,7 +5011,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5016,7 +5021,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5042,38 +5047,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708138</t>
+          <t>https://artportalen.se/Sighting/135708151</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135708162</v>
+        <v>135708154</v>
       </c>
       <c r="B41" t="n">
-        <v>79477</v>
+        <v>98182</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5083,10 +5088,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855298</v>
+        <v>855402</v>
       </c>
       <c r="R41" t="n">
-        <v>7538605</v>
+        <v>7538970</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5118,7 +5123,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5128,7 +5133,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5154,38 +5159,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135708162</t>
+          <t>https://artportalen.se/Sighting/135708154</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135708168</v>
+        <v>135708156</v>
       </c>
       <c r="B42" t="n">
-        <v>79477</v>
+        <v>98182</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855550</v>
+        <v>855399</v>
       </c>
       <c r="R42" t="n">
-        <v>7538342</v>
+        <v>7538944</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5230,7 +5235,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5240,7 +5245,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5265,6 +5270,790 @@
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135708156</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135708157</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98182</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Parkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>855322</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7538890</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135708157</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135708159</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98182</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Parkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>855323</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7538767</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135708159</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135708111</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79477</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Parkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>855791</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7538224</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135708111</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135708121</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79477</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Parkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>855784</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7538250</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135708121</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135708138</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79477</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Parkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>855768</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7538350</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135708138</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135708162</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79477</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Parkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>855298</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7538605</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135708162</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135708168</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79477</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Parkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>855550</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7538342</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135708168</t>
         </is>
@@ -5313,6 +6102,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57883-2025 artfynd.xlsx
+++ b/artfynd/A 57883-2025 artfynd.xlsx
@@ -4043,7 +4043,7 @@
         <v>135708112</v>
       </c>
       <c r="B32" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135708120</v>
       </c>
       <c r="B33" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135708141</v>
       </c>
       <c r="B34" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135708144</v>
       </c>
       <c r="B35" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135708145</v>
       </c>
       <c r="B36" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135708188</v>
       </c>
       <c r="B37" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135708191</v>
       </c>
       <c r="B38" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
